--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -880,7 +888,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>634-559-CM26</t>
+          <t>1093219-20-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,12 +913,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,28 +928,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10359.2</v>
+        <v>72581.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1093219-20-CM26</t>
+          <t>1641-19986-SE26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,12 +978,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,28 +993,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>72581.2</v>
+        <v>1535.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>711-98-CM26</t>
+          <t>1641-19983-SE26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1043,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,28 +1058,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>604207.36</v>
+        <v>1535.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1469-2066-CM26</t>
+          <t>1641-19984-SE26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,43 +1108,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>301884.06</v>
+        <v>1535.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1077195-67-CM26</t>
+          <t>634-559-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1163,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1173,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,28 +1188,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>25603.08</v>
+        <v>10359.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1013353-81-CM26</t>
+          <t>1469-2066-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1228,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,43 +1238,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.154.021-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>39484.9</v>
+        <v>301884.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1301883-195-CM26</t>
+          <t>711-98-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1293,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1303,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1318,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.802.163-5</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1333,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>15929.54</v>
+        <v>604207.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>750998-112-CM26</t>
+          <t>1641-19980-SE26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1354,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1364,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.255.100-1</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1379,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14442.64</v>
+        <v>1535.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>937232-679-CM26</t>
+          <t>1077195-67-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1429,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1444,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD LIGARIUS SPA</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.063.547-0</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1459,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>55449.26</v>
+        <v>25603.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>608897-243-CM26</t>
+          <t>1013353-81-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1480,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1490,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>65.154.021-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1505,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1520,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10167.47</v>
+        <v>39484.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2686-574-CM26</t>
+          <t>1301883-195-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1541,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1551,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1566,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>UBIQUITY SPA</t>
+          <t>SERVICIOS INFORMÁTICOS COMMUNITY MARKETPLACE LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.423.027-2</t>
+          <t>76.802.163-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1581,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13448.93</v>
+        <v>15929.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>608897-244-CM26</t>
+          <t>750998-112-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1602,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,27 +1612,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>69.255.100-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>I MUNICIPALIDAD DE LO ESPEJO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1642,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>24415.6</v>
+        <v>14442.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1602-102-CM26</t>
+          <t>937232-679-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1663,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1673,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1688,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1703,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30345.43</v>
+        <v>55449.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1425525-27-CM26</t>
+          <t>608897-243-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1734,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.560-6</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1749,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1764,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>77987.85000000001</v>
+        <v>10167.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1005498-132-CM26</t>
+          <t>2686-574-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1795,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1810,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>UBIQUITY SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.423.027-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1825,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>24744.2</v>
+        <v>13448.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>797305-53-CM26</t>
+          <t>608897-244-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1856,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ANIDA CONSULTORES S A</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.680.090-2</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1886,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>47299.75</v>
+        <v>24415.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>609-170-CM26</t>
+          <t>1602-102-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1917,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1932,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SILOCYDATA SPA</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.185.932-1</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1947,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36448.37</v>
+        <v>30345.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>586-410-CM26</t>
+          <t>1425525-27-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,43 +1978,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>62.000.560-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.733.311-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>16165.58</v>
+        <v>77987.85000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1005498-135-CM26</t>
+          <t>1005498-132-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2033,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,28 +2058,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.561.404-k</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>74517.17999999999</v>
+        <v>24744.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2268-138-CM26</t>
+          <t>797305-53-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2098,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2108,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2123,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CRUD SPA</t>
+          <t>ANIDA CONSULTORES S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.142.835-5</t>
+          <t>77.680.090-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2138,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>73043.13</v>
+        <v>47299.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2423-1215-CM26</t>
+          <t>586-410-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2159,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,43 +2169,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.072.100-7</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>201000.94</v>
+        <v>16165.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>599-170-CM26</t>
+          <t>609-170-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2224,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2234,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,28 +2249,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
+          <t>SILOCYDATA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.108.701-0</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.185.932-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>40630.13</v>
+        <v>36448.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1591-175-CM26</t>
+          <t>1005498-135-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2289,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2299,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2314,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>SOCIEDAD COMPUTACIONAL INDEXAR SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
+          <t>76.561.404-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2329,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>14412.21</v>
+        <v>74517.17999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>870-209-CM26</t>
+          <t>2268-138-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2350,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2375,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CRUD SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>77.142.835-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2390,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>177904.1</v>
+        <v>73043.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>869591-40-CM26</t>
+          <t>2423-1215-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2411,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2421,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>69.072.100-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2436,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>71839.14999999999</v>
+        <v>201000.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1019-318-CM26</t>
+          <t>1591-175-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2472,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2482,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2497,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>39907.41</v>
+        <v>14412.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1469-2745-CM26</t>
+          <t>599-170-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2537,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,27 +2547,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.108.701-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2577,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>23046.81</v>
+        <v>40630.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>601-181-CM26</t>
+          <t>870-209-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2598,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.819.000-7</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SALUD</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2623,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2638,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7373.55</v>
+        <v>177904.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>770-129-CM26</t>
+          <t>869591-40-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2659,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2669,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2684,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15107.91</v>
+        <v>71839.14999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>761-270-CM26</t>
+          <t>1019-318-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2724,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2734,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2749,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2764,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>128378.79</v>
+        <v>39907.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1067455-102-CM26</t>
+          <t>1499-4833-SE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2785,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,28 +2810,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>76.227.643-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>47196.2</v>
+        <v>4816.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>730566-175-CM26</t>
+          <t>2770-320-SE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2850,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2860,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2875,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>301925.55</v>
+        <v>52929.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1339159-83-CM26</t>
+          <t>1469-2745-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2915,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,43 +2925,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>240698.07</v>
+        <v>23046.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1973-2917-CM26</t>
+          <t>770-129-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2980,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2990,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +3005,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +3020,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19487.2</v>
+        <v>15107.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2147-435-CM26</t>
+          <t>601-181-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3041,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,43 +3051,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>60.819.000-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>10377.35</v>
+        <v>7373.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1098710-303-CM26</t>
+          <t>761-270-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3106,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3116,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3131,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3146,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>20884.28</v>
+        <v>128378.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1393575-84-CM26</t>
+          <t>1067455-102-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3167,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3177,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8486.870000000001</v>
+        <v>47196.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4931-114-CM26</t>
+          <t>730566-175-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3238,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,28 +3253,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>274977.66</v>
+        <v>301925.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1375735-48-CM26</t>
+          <t>1339159-83-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3293,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,43 +3303,47 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>51168.17</v>
+        <v>240698.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>610-58-CM26</t>
+          <t>1973-2917-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3358,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3368,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3383,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3398,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13869.74</v>
+        <v>19487.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2766-572-CM26</t>
+          <t>2147-435-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3419,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,27 +3429,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3459,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8351.34</v>
+        <v>10377.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5153-1605-CM26</t>
+          <t>1098710-303-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3480,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3490,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,28 +3505,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>37202.6</v>
+        <v>20884.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1314-26-CM26</t>
+          <t>1393575-84-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3545,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3555,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,20 +3578,24 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16816.99</v>
+        <v>8486.870000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1393093-777-CM26</t>
+          <t>4931-114-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3610,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,43 +3620,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>65.613.130-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>26162.38</v>
+        <v>274977.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1725-893-CM26</t>
+          <t>1375735-48-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3675,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3685,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3715,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7026.13</v>
+        <v>51168.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5537-221-CM26</t>
+          <t>610-58-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3736,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3746,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3761,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3776,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>14834.83</v>
+        <v>13869.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5403-68-CM26</t>
+          <t>2766-572-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3797,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3807,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,28 +3822,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>129683.94</v>
+        <v>8351.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>609-237-CM26</t>
+          <t>5153-1605-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3862,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3887,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32677.65</v>
+        <v>37202.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>895072-174-CM26</t>
+          <t>1314-26-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3927,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3937,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3856,20 +3960,24 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>28072</v>
+        <v>16816.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5514-70-CM26</t>
+          <t>1393093-777-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3992,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,43 +4002,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>54656.28</v>
+        <v>26162.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>765-194-CM26</t>
+          <t>1725-893-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +4057,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +4067,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14788.38</v>
+        <v>7026.13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1385462-179-CM26</t>
+          <t>5537-221-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4122,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4132,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4147,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>SPIELUP SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.582.047-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4162,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>42812.45</v>
+        <v>14834.83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>622844-25-CM26</t>
+          <t>5403-68-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4183,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4193,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4208,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.554.706-7</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4223,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>31211.63</v>
+        <v>129683.94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1016-89-CM26</t>
+          <t>609-237-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,37 +4244,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4284,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>15439.79</v>
+        <v>32677.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>599-183-CM26</t>
+          <t>5514-70-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4305,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4315,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DEEPSOURCE SERVICIOS INTEGRALES SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.842.278-8</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4345,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>23634.76</v>
+        <v>54656.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4389-81-CM26</t>
+          <t>895072-174-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4366,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4376,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,28 +4391,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>20949.94</v>
+        <v>28072</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1078113-23-CM26</t>
+          <t>765-194-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4431,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,27 +4441,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4471,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>34837.47</v>
+        <v>14788.38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2735-1241-CM26</t>
+          <t>1385462-179-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4492,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4502,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4517,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SOAINT GESTION S.A.</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.829.360-5</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4532,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>31429.4</v>
+        <v>42812.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>593951-312-CM26</t>
+          <t>622844-25-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4553,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4563,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,28 +4578,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>76.554.706-7</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41882.94</v>
+        <v>31211.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1082957-287-CM26</t>
+          <t>1016-89-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4618,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,43 +4628,47 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.680-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ZerviZ</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.755.489-3</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13441.15</v>
+        <v>15439.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1602-108-CM26</t>
+          <t>599-183-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4683,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4693,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4708,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>DEEPSOURCE SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
+          <t>76.842.278-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,7 +4723,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>25235.17</v>
+        <v>23634.76</v>
       </c>
     </row>
     <row r="69">
@@ -4649,7 +4777,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4662,7 +4794,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1016-93-CM26</t>
+          <t>1078113-23-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4809,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4819,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4834,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ORITEC</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.405.003-7</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4849,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>62275.83</v>
+        <v>34837.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5518-102-CM26</t>
+          <t>2735-1241-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4870,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4880,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4895,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Taller Digital</t>
+          <t>SOAINT GESTION S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.433.976-2</t>
+          <t>96.829.360-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4910,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>30121.7</v>
+        <v>31429.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1016-90-CM26</t>
+          <t>4389-81-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4931,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,27 +4941,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4971,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>36548.13</v>
+        <v>20949.94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1111089-291-CM26</t>
+          <t>593951-312-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4992,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +5002,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,28 +5017,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>48124.15</v>
+        <v>41882.94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1725-950-CM26</t>
+          <t>1082957-287-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +5057,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,27 +5067,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>62.000.680-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.755.489-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,6 +5097,445 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
+        <v>13441.15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2429-1208-SE26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>23439.34</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1602-108-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>VAB Ingeniería de Software Limitada</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.090.261-6</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>25235.17</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1016-93-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ORITEC</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.405.003-7</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>62275.83</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5518-102-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Taller Digital</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.433.976-2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>30121.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1016-90-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>USERCODE SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>36548.13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1111089-291-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>48124.15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1725-950-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
         <v>22820.37</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>586-410-CM26</t>
+          <t>609-170-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>XMS Business Solutions S.A.</t>
+          <t>SILOCYDATA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.249.938-k</t>
+          <t>77.185.932-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>16165.58</v>
+        <v>36448.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>609-170-CM26</t>
+          <t>586-410-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2229,32 +2229,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SILOCYDATA SPA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.185.932-1</t>
+          <t>76.249.938-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>36448.37</v>
+        <v>16165.58</v>
       </c>
     </row>
     <row r="30">
@@ -2335,7 +2335,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2268-138-CM26</t>
+          <t>3328-2102-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CRUD SPA</t>
+          <t>INDRA SISTEMAS CHILE S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.142.835-5</t>
+          <t>96.851.110-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>73043.13</v>
+        <v>37976.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2423-1215-CM26</t>
+          <t>2268-138-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.072.100-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>CRUD SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.142.835-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>201000.94</v>
+        <v>73043.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1591-175-CM26</t>
+          <t>2423-1215-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>69.072.100-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2497,32 +2497,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14412.21</v>
+        <v>201000.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>599-170-CM26</t>
+          <t>1591-175-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2547,12 +2543,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2562,28 +2558,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.108.701-0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>40630.13</v>
+        <v>14412.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>870-209-CM26</t>
+          <t>599-170-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>GUADALTEL CHILE SERVICIOS DE INFORMACION LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.108.701-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>177904.1</v>
+        <v>40630.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>869591-40-CM26</t>
+          <t>870-209-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2664,17 +2664,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.808.000-7</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2684,32 +2684,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.130.712-6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>71839.14999999999</v>
+        <v>177904.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1019-318-CM26</t>
+          <t>869591-40-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2734,12 +2730,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.808.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2749,28 +2745,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39907.41</v>
+        <v>71839.14999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1499-4833-SE26</t>
+          <t>1019-318-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2790,17 +2790,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.608.402-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DEL TORAX</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2810,32 +2810,28 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Lahuen Health Services SpA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.227.643-7</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.014.934-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4816.7</v>
+        <v>39907.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2770-320-SE26</t>
+          <t>1499-4833-SE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2850,22 +2846,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.070.900-7</t>
+          <t>61.608.402-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAIPU</t>
+          <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2875,12 +2871,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.227.643-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2894,13 +2890,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>52929.08</v>
+        <v>4816.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1469-2745-CM26</t>
+          <t>2770-320-SE26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2925,27 +2921,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.070.900-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE MAIPU</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2959,13 +2955,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>23046.81</v>
+        <v>52929.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>770-129-CM26</t>
+          <t>1469-2745-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2980,7 +2976,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2990,43 +2986,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>15107.91</v>
+        <v>23046.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>601-181-CM26</t>
+          <t>770-129-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.819.000-7</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SALUD</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3066,32 +3066,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.185.219-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7373.55</v>
+        <v>15107.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>761-270-CM26</t>
+          <t>601-181-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3116,12 +3112,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.819.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3131,28 +3127,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>128378.79</v>
+        <v>7373.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1067455-102-CM26</t>
+          <t>761-270-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.420-0</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>APHIX INFORMATICA LIMITADA</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.170.582-2</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3207,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>47196.2</v>
+        <v>128378.79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>730566-175-CM26</t>
+          <t>1067455-102-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>62.000.420-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>SUBSECRETARIA DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3253,32 +3253,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.170.582-2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>301925.55</v>
+        <v>47196.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1339159-83-CM26</t>
+          <t>730566-175-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3303,12 +3299,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.070-8</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3318,12 +3314,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3337,13 +3333,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>240698.07</v>
+        <v>301925.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1973-2917-CM26</t>
+          <t>1339159-83-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3368,12 +3364,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>61.981.070-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3383,28 +3379,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>19487.2</v>
+        <v>240698.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2147-435-CM26</t>
+          <t>1973-2917-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.406-1</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10377.35</v>
+        <v>19487.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1098710-303-CM26</t>
+          <t>2147-435-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3490,47 +3490,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>61.606.406-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL COMB</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>20884.28</v>
+        <v>10377.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1393575-84-CM26</t>
+          <t>1098710-303-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3555,12 +3551,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3570,12 +3566,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3589,13 +3585,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>8486.870000000001</v>
+        <v>20884.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4931-114-CM26</t>
+          <t>1393575-84-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3620,12 +3616,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>65.613.130-6</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3635,12 +3631,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3654,13 +3650,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>274977.66</v>
+        <v>8486.870000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1375735-48-CM26</t>
+          <t>4931-114-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3675,7 +3671,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3685,43 +3681,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>65.613.130-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>COMISION ADMINISTRADORA DEL SISTEMA DE CREDITOS P. ESTUDIOS SUPERIORES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>51168.17</v>
+        <v>274977.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>610-58-CM26</t>
+          <t>1375735-48-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3746,27 +3746,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3776,13 +3776,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>13869.74</v>
+        <v>51168.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2766-572-CM26</t>
+          <t>610-58-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3822,32 +3822,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.528.848-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8351.34</v>
+        <v>13869.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5153-1605-CM26</t>
+          <t>2766-572-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3862,7 +3858,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3872,12 +3868,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3887,12 +3883,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3906,13 +3902,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>37202.6</v>
+        <v>8351.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1314-26-CM26</t>
+          <t>5153-1605-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3937,12 +3933,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3952,12 +3948,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.063.770-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3971,13 +3967,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>16816.99</v>
+        <v>37202.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1393093-777-CM26</t>
+          <t>1314-26-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4002,27 +3998,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4036,13 +4032,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>26162.38</v>
+        <v>16816.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1725-893-CM26</t>
+          <t>1393093-777-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4067,27 +4063,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4101,13 +4097,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7026.13</v>
+        <v>26162.38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5537-221-CM26</t>
+          <t>1725-893-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4122,7 +4118,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4132,43 +4128,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SPIELUP SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.582.047-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>14834.83</v>
+        <v>7026.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5403-68-CM26</t>
+          <t>5537-221-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>SPIELUP SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
+          <t>76.582.047-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>129683.94</v>
+        <v>14834.83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>609-237-CM26</t>
+          <t>5403-68-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4244,22 +4244,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.004.023-1</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4284,13 +4284,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>32677.65</v>
+        <v>129683.94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5514-70-CM26</t>
+          <t>609-237-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>ENTELGY CHILE CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.004.023-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4345,13 +4345,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>54656.28</v>
+        <v>32677.65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>895072-174-CM26</t>
+          <t>5514-70-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4376,47 +4376,43 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.466.220-9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>28072</v>
+        <v>54656.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>765-194-CM26</t>
+          <t>895072-174-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4431,7 +4427,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4441,43 +4437,47 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>14788.38</v>
+        <v>28072</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1385462-179-CM26</t>
+          <t>765-194-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4502,27 +4502,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>42812.45</v>
+        <v>14788.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>622844-25-CM26</t>
+          <t>1385462-179-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4578,32 +4578,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.554.706-7</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.528.848-7</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>31211.63</v>
+        <v>42812.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1016-89-CM26</t>
+          <t>622844-25-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4628,27 +4624,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>76.554.706-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4662,13 +4658,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>15439.79</v>
+        <v>31211.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>599-183-CM26</t>
+          <t>1016-89-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4693,43 +4689,47 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DEEPSOURCE SERVICIOS INTEGRALES SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.842.278-8</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>23634.76</v>
+        <v>15439.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>606-375-CM26</t>
+          <t>599-183-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4769,32 +4769,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>DEEPSOURCE SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.842.278-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>12951.04</v>
+        <v>23634.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1078113-23-CM26</t>
+          <t>606-375-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4819,12 +4815,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4834,28 +4830,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.528.848-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>34837.47</v>
+        <v>12951.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2735-1241-CM26</t>
+          <t>1078113-23-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOAINT GESTION S.A.</t>
+          <t>RESPUESTAS DE TECNOLOGIA DE LA INFORMACION S.P.A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.829.360-5</t>
+          <t>76.528.848-7</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>31429.4</v>
+        <v>34837.47</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4389-81-CM26</t>
+          <t>2735-1241-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>SOAINT GESTION S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>96.829.360-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4971,13 +4971,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>20949.94</v>
+        <v>31429.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>593951-312-CM26</t>
+          <t>4389-81-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5017,32 +5017,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.173.545-2</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.198.095-5</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41882.94</v>
+        <v>20949.94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1082957-287-CM26</t>
+          <t>593951-312-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5067,12 +5063,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>62.000.680-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5082,28 +5078,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ZerviZ</t>
+          <t>SOCIEDAD DE PROFESIONALES ON DEMAND AND RECURRING IT SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.755.489-3</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>77.173.545-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>13441.15</v>
+        <v>41882.94</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2429-1208-SE26</t>
+          <t>1082957-287-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5128,47 +5128,43 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.680-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>ZerviZ</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.755.489-3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>23439.34</v>
+        <v>13441.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1602-108-CM26</t>
+          <t>2429-1208-SE26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5188,48 +5184,52 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25235.17</v>
+        <v>23439.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1016-93-CM26</t>
+          <t>1602-108-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ORITEC</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.405.003-7</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5284,13 +5284,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>62275.83</v>
+        <v>25235.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5518-102-CM26</t>
+          <t>1016-93-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Taller Digital</t>
+          <t>ORITEC</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.433.976-2</t>
+          <t>76.405.003-7</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>30121.7</v>
+        <v>62275.83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1016-90-CM26</t>
+          <t>5518-102-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5376,47 +5376,43 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>Taller Digital</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.433.976-2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>36548.13</v>
+        <v>30121.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1111089-291-CM26</t>
+          <t>1016-90-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5441,101 +5437,166 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>48124.15</v>
+        <v>36548.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>1111089-291-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.915.000-9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.444.489-2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>48124.15</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>1725-950-CM26</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>60.901.002-9</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>SAARGO SPA</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="n">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>22820.37</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2026.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
